--- a/public/templates/examples/A-020-RTORPODocumentation-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-020-RTORPODocumentation-EXAMPLE-M.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -186,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -248,6 +250,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,7 +635,7 @@
     <row r="2" ht="29.75" customHeight="1">
       <c r="A2" s="8" t="n"/>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -734,7 +739,7 @@
     <row r="16" ht="29.75" customHeight="1">
       <c r="A16" s="8" t="n"/>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>System or service \ Recovery attribute</t>
@@ -761,7 +766,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>9-1-1 call handling / call delivery</t>
@@ -788,7 +793,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="34.7" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Computer-aided dispatch (CAD)</t>
@@ -815,7 +820,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Radio / dispatch console</t>
@@ -842,7 +847,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="34.7" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Mapping / GIS / ALI</t>
@@ -869,7 +874,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Voice logging</t>
@@ -896,7 +901,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="34.7" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Administrative / records</t>
@@ -1025,10 +1030,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="B42" s="24">
+        <v>46037</v>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
@@ -1043,11 +1046,11 @@
       <c r="E42" s="14" t="n"/>
     </row>
     <row r="43"/>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="2" t="n"/>
+    <row r="44">
+      <c r="A44"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A15:E15"/>
@@ -1075,12 +1078,11 @@
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>